--- a/InputData/elec/CRpUNL/Cap Ret per Unit Net Loss.xlsx
+++ b/InputData/elec/CRpUNL/Cap Ret per Unit Net Loss.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us-analysis\InputData\elec\CRpUNL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\CRpUNL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6567EA64-6F7D-43AE-A26B-B09A74E72F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB258EB6-E305-4F69-9AA4-CC8C104FA1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{67B50A2A-83E2-40E1-A966-DC033ADD8EBF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{67B50A2A-83E2-40E1-A966-DC033ADD8EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -525,14 +525,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B7A547-DAFD-4CBC-90C6-A86A1413C282}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -540,42 +540,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -591,12 +591,12 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
@@ -604,42 +604,42 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
         <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4">
         <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
         <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -647,25 +647,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7">
         <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8">
         <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -697,34 +697,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
         <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
         <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15">
         <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -748,67 +748,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19">
-        <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" ref="B19:B25" si="0">$B$2</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20">
-        <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21">
-        <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22">
-        <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>24</v>
       </c>
       <c r="B23">
-        <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B24">
-        <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B25">
-        <f>$B$2</f>
-        <v>1.4999999999999999E-2</v>
+        <f t="shared" si="0"/>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
   </sheetData>
